--- a/Documents/Product Catalog/Home/Kids Bed.xlsx
+++ b/Documents/Product Catalog/Home/Kids Bed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392F19AF-EE76-42E9-8D80-43C67B3B03BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B05110-D106-4227-AEC0-9ADC0ADFAA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kids Bed" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -285,7 +285,22 @@
 Perfect for children's bedrooms, playrooms, daycare centers, and modern family homes, this nature-themed single bed brings together comfort, safety, and timeless design to create a cozy space where children can sleep, play, and dream.</t>
   </si>
   <si>
-    <t>বেড</t>
+    <t>সানরে বেড</t>
+  </si>
+  <si>
+    <t>প্রিন্সেস বেড</t>
+  </si>
+  <si>
+    <t>হ্যালো কিটি বেড</t>
+  </si>
+  <si>
+    <t>স্কাইবো বেড</t>
+  </si>
+  <si>
+    <t>পোকো বেড</t>
+  </si>
+  <si>
+    <t>মোয়ানা মোয়ানা বেড</t>
   </si>
 </sst>
 </file>
@@ -598,23 +613,6 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -626,6 +624,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1461,89 +1476,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="22" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="29"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="22" t="s">
+      <c r="L3" s="32"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="26" t="s">
         <v>14</v>
       </c>
       <c r="S3" s="4"/>
@@ -1576,11 +1591,11 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
@@ -1590,8 +1605,8 @@
       <c r="H4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="26"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="31"/>
       <c r="K4" s="5" t="s">
         <v>18</v>
       </c>
@@ -1601,10 +1616,10 @@
       <c r="M4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -1722,7 +1737,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -1802,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
@@ -1882,7 +1897,7 @@
         <v>45</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
@@ -1962,7 +1977,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9" t="s">
@@ -2042,7 +2057,7 @@
         <v>54</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
